--- a/output/pdf_financials_xlsx/MPTH.H.xlsx
+++ b/output/pdf_financials_xlsx/MPTH.H.xlsx
@@ -1303,7 +1303,7 @@
         <v>-0.114568</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.14067</v>
+        <v>-0.14067</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>-0.114568</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.14067</v>
+        <v>-0.14067</v>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>-0.114568</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.14067</v>
+        <v>-0.14067</v>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>5.7284</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-2.8134</v>
+        <v>2.8134</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>-0.114568</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.14067</v>
+        <v>-0.14067</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>-0.114568</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.14067</v>
+        <v>-0.14067</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
@@ -5785,46 +5785,46 @@
         <v>3.909512</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.909511</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.909511</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.909511</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.975635</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.975635</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.975635</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.975635</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.975635</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.975635</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.975635</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.975635</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.983637</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.983637</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.007599</v>
       </c>
     </row>
     <row r="93">
@@ -6134,7 +6134,7 @@
         <v>0.848679</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.845232</v>
+        <v>-0.845232</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.172037</v>
@@ -9494,7 +9494,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -10676,7 +10680,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -11404,7 +11412,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -12308,7 +12320,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -12398,7 +12414,11 @@
           <t>Share based payment reserve 4</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -12878,7 +12898,11 @@
           <t>Share based payment reserves</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -21518,7 +21542,7 @@
         </is>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.845232</v>
+        <v>-0.845232</v>
       </c>
       <c r="H137" s="5" t="n">
         <v>-0.172037</v>
@@ -31444,7 +31468,7 @@
         </is>
       </c>
       <c r="M240" s="5" t="n">
-        <v>0.14067</v>
+        <v>-0.14067</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -32791,10 +32815,10 @@
         </is>
       </c>
       <c r="L254" s="5" t="n">
-        <v>0.114568</v>
+        <v>-0.114568</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.14067</v>
+        <v>-0.14067</v>
       </c>
       <c r="N254" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MPTH.H.xlsx
+++ b/output/pdf_financials_xlsx/MPTH.H.xlsx
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000508</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.001192</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000262</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>8.2e-05</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000492</v>
       </c>
     </row>
     <row r="13">
@@ -2037,19 +2037,19 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.06976300000000001</v>
+        <v>-0.070271</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.134164</v>
+        <v>-0.135356</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.091777</v>
+        <v>-0.092039</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.089394</v>
+        <v>-0.089476</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.147986</v>
+        <v>-0.148478</v>
       </c>
     </row>
     <row r="28">
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.06976300000000001</v>
+        <v>-0.070271</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.134164</v>
+        <v>-0.135356</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.091777</v>
+        <v>-0.092039</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.089394</v>
+        <v>-0.089476</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.147986</v>
+        <v>-0.148478</v>
       </c>
     </row>
     <row r="30">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.032911</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.032911</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -2429,19 +2429,19 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.04239</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.027395</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.016948</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000376</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000301</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.420842</v>
@@ -2462,7 +2462,7 @@
         <v>0.000114</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.305216</v>
       </c>
     </row>
     <row r="35">
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.032911</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.032911</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -2539,19 +2539,19 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.04239</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.027395</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.016948</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000376</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000301</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.420842</v>
@@ -2572,7 +2572,7 @@
         <v>0.000114</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.305216</v>
       </c>
     </row>
     <row r="37">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.268707</v>
+        <v>1.235796</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -27612,7 +27612,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -27708,7 +27708,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -29870,7 +29870,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -29968,7 +29968,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -30448,7 +30448,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">

--- a/output/pdf_financials_xlsx/MPTH.H.xlsx
+++ b/output/pdf_financials_xlsx/MPTH.H.xlsx
@@ -6192,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.098526</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.019727</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -23852,7 +23852,11 @@
           <t>Loss on disposal of property and equipment -</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -38932,7 +38936,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
